--- a/backend/data/financials_by_company/002010.SZ.xlsx
+++ b/backend/data/financials_by_company/002010.SZ.xlsx
@@ -4184,187 +4184,187 @@
       </c>
       <c r="DL1" t="inlineStr">
         <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>epsForward</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EF1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EG1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EH1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="EI1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="EJ1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="EK1" t="inlineStr">
+        <is>
           <t>shortName</t>
         </is>
       </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
+      <c r="EL1" t="inlineStr">
         <is>
           <t>corporateActions</t>
         </is>
       </c>
-      <c r="DO1" t="inlineStr">
+      <c r="EM1" t="inlineStr">
         <is>
           <t>regularMarketTime</t>
         </is>
       </c>
-      <c r="DP1" t="inlineStr">
+      <c r="EN1" t="inlineStr">
         <is>
           <t>exchange</t>
         </is>
       </c>
-      <c r="DQ1" t="inlineStr">
+      <c r="EO1" t="inlineStr">
         <is>
           <t>messageBoardId</t>
         </is>
       </c>
-      <c r="DR1" t="inlineStr">
+      <c r="EP1" t="inlineStr">
         <is>
           <t>exchangeTimezoneName</t>
         </is>
       </c>
-      <c r="DS1" t="inlineStr">
+      <c r="EQ1" t="inlineStr">
         <is>
           <t>exchangeTimezoneShortName</t>
         </is>
       </c>
-      <c r="DT1" t="inlineStr">
+      <c r="ER1" t="inlineStr">
         <is>
           <t>gmtOffSetMilliseconds</t>
         </is>
       </c>
-      <c r="DU1" t="inlineStr">
+      <c r="ES1" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="DV1" t="inlineStr">
+      <c r="ET1" t="inlineStr">
         <is>
           <t>esgPopulated</t>
         </is>
       </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
+      <c r="EU1" t="inlineStr">
         <is>
           <t>hasPrePostMarketData</t>
         </is>
       </c>
-      <c r="ED1" t="inlineStr">
+      <c r="EV1" t="inlineStr">
         <is>
           <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="EL1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="EM1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="EN1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="EO1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="EP1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="EQ1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="ER1" t="inlineStr">
-        <is>
-          <t>epsForward</t>
-        </is>
-      </c>
-      <c r="ES1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="ET1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EU1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EV1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
         </is>
       </c>
       <c r="EW1" t="inlineStr">
@@ -4459,73 +4459,73 @@
         <v>4</v>
       </c>
       <c r="S2" t="n">
-        <v>4.89</v>
+        <v>4.65</v>
       </c>
       <c r="T2" t="n">
-        <v>4.86</v>
+        <v>4.75</v>
       </c>
       <c r="U2" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="V2" t="n">
         <v>4.72</v>
       </c>
-      <c r="V2" t="n">
-        <v>4.89</v>
-      </c>
       <c r="W2" t="n">
-        <v>4.89</v>
+        <v>4.65</v>
       </c>
       <c r="X2" t="n">
-        <v>4.86</v>
+        <v>4.75</v>
       </c>
       <c r="Y2" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="Z2" t="n">
         <v>4.72</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>4.89</v>
       </c>
       <c r="AA2" t="n">
         <v>0.15</v>
       </c>
       <c r="AB2" t="n">
-        <v>3.07</v>
+        <v>3.23</v>
       </c>
       <c r="AC2" t="n">
-        <v>1761782400</v>
+        <v>1782777600</v>
       </c>
       <c r="AD2" t="n">
         <v>0.6292</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.663</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="AG2" t="n">
-        <v>20.375</v>
+        <v>19.583332</v>
       </c>
       <c r="AH2" t="n">
-        <v>17.464285</v>
+        <v>16.785713</v>
       </c>
       <c r="AI2" t="n">
-        <v>26423181</v>
+        <v>21201701</v>
       </c>
       <c r="AJ2" t="n">
-        <v>26423181</v>
+        <v>21201701</v>
       </c>
       <c r="AK2" t="n">
-        <v>23143759</v>
+        <v>22822682</v>
       </c>
       <c r="AL2" t="n">
-        <v>19940592</v>
+        <v>21701457</v>
       </c>
       <c r="AM2" t="n">
-        <v>19940592</v>
+        <v>21701457</v>
       </c>
       <c r="AN2" t="n">
-        <v>4.88</v>
+        <v>4.69</v>
       </c>
       <c r="AO2" t="n">
-        <v>4.89</v>
+        <v>4.7</v>
       </c>
       <c r="AP2" t="n">
         <v>0</v>
@@ -4534,13 +4534,13 @@
         <v>0</v>
       </c>
       <c r="AR2" t="n">
-        <v>13516110848</v>
+        <v>12990945280</v>
       </c>
       <c r="AS2" t="n">
-        <v>13516111140</v>
+        <v>12659261558</v>
       </c>
       <c r="AT2" t="n">
-        <v>4.72</v>
+        <v>4.44</v>
       </c>
       <c r="AU2" t="n">
         <v>7.39</v>
@@ -4552,19 +4552,19 @@
         <v>1.675</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.58714414</v>
+        <v>0.5643308</v>
       </c>
       <c r="AY2" t="n">
-        <v>5.491</v>
+        <v>5.276</v>
       </c>
       <c r="AZ2" t="n">
-        <v>6.03575</v>
+        <v>5.9609</v>
       </c>
       <c r="BA2" t="n">
         <v>0.15</v>
       </c>
       <c r="BB2" t="n">
-        <v>0.030674849</v>
+        <v>0.032258064</v>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
@@ -4575,22 +4575,22 @@
         <v>0</v>
       </c>
       <c r="BE2" t="n">
-        <v>24954761216</v>
+        <v>24429594624</v>
       </c>
       <c r="BF2" t="n">
         <v>0.02863</v>
       </c>
       <c r="BG2" t="n">
-        <v>1109620208</v>
+        <v>1130018756</v>
       </c>
       <c r="BH2" t="n">
         <v>2764030908</v>
       </c>
       <c r="BI2" t="n">
-        <v>0.61175</v>
+        <v>0.61573005</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.01417</v>
+        <v>0.00957</v>
       </c>
       <c r="BK2" t="n">
         <v>2764030908</v>
@@ -4599,7 +4599,7 @@
         <v>6.57</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.7442922</v>
+        <v>0.71537286</v>
       </c>
       <c r="BN2" t="n">
         <v>1767139200</v>
@@ -4631,22 +4631,22 @@
         <v>1305763200</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.084</v>
+        <v>1.061</v>
       </c>
       <c r="BX2" t="n">
-        <v>18.929</v>
+        <v>18.531</v>
       </c>
       <c r="BY2" t="n">
-        <v>-0.073863626</v>
+        <v>-0.17112297</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0.24487448</v>
+        <v>0.20116603</v>
       </c>
       <c r="CA2" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="CB2" t="n">
-        <v>1761782400</v>
+        <v>1782777600</v>
       </c>
       <c r="CC2" t="inlineStr">
         <is>
@@ -4654,7 +4654,7 @@
         </is>
       </c>
       <c r="CD2" t="n">
-        <v>4.89</v>
+        <v>4.7</v>
       </c>
       <c r="CE2" t="n">
         <v>6.58</v>
@@ -4773,138 +4773,138 @@
       </c>
       <c r="DL2" t="inlineStr">
         <is>
+          <t>Transfar Zhilian Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="DM2" t="n">
+        <v>1.0752627</v>
+      </c>
+      <c r="DN2" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="DO2" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="DP2" t="n">
+        <v>0.049999714</v>
+      </c>
+      <c r="DQ2" t="inlineStr">
+        <is>
+          <t>4.64 - 4.72</t>
+        </is>
+      </c>
+      <c r="DR2" t="inlineStr">
+        <is>
+          <t>Shenzhen</t>
+        </is>
+      </c>
+      <c r="DS2" t="n">
+        <v>22822682</v>
+      </c>
+      <c r="DT2" t="n">
+        <v>0.25999975</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>0.0585585</v>
+      </c>
+      <c r="DV2" t="inlineStr">
+        <is>
+          <t>4.44 - 7.39</t>
+        </is>
+      </c>
+      <c r="DW2" t="n">
+        <v>-2.69</v>
+      </c>
+      <c r="DX2" t="n">
+        <v>-0.36400542</v>
+      </c>
+      <c r="DY2" t="n">
+        <v>-17.112297</v>
+      </c>
+      <c r="DZ2" t="n">
+        <v>1651229940</v>
+      </c>
+      <c r="EA2" t="n">
+        <v>1651492800</v>
+      </c>
+      <c r="EB2" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="EC2" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="ED2" t="n">
+        <v>-0.5760002</v>
+      </c>
+      <c r="EE2" t="n">
+        <v>-0.109173656</v>
+      </c>
+      <c r="EF2" t="n">
+        <v>-1.2609</v>
+      </c>
+      <c r="EG2" t="n">
+        <v>-0.21152847</v>
+      </c>
+      <c r="EH2" t="n">
+        <v>15</v>
+      </c>
+      <c r="EI2" t="n">
+        <v>15</v>
+      </c>
+      <c r="EJ2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EK2" t="inlineStr">
+        <is>
           <t>TRANSFAR ZHILIAN CO LTD</t>
         </is>
       </c>
-      <c r="DM2" t="inlineStr">
-        <is>
-          <t>Transfar Zhilian Co., Ltd.</t>
-        </is>
-      </c>
-      <c r="DN2" t="inlineStr">
+      <c r="EL2" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="DO2" t="n">
-        <v>1782111885</v>
-      </c>
-      <c r="DP2" t="inlineStr">
+      <c r="EM2" t="n">
+        <v>1783062276</v>
+      </c>
+      <c r="EN2" t="inlineStr">
         <is>
           <t>SHZ</t>
         </is>
       </c>
-      <c r="DQ2" t="inlineStr">
+      <c r="EO2" t="inlineStr">
         <is>
           <t>finmb_303901165</t>
         </is>
       </c>
-      <c r="DR2" t="inlineStr">
+      <c r="EP2" t="inlineStr">
         <is>
           <t>Asia/Shanghai</t>
         </is>
       </c>
-      <c r="DS2" t="inlineStr">
+      <c r="EQ2" t="inlineStr">
         <is>
           <t>CST</t>
         </is>
       </c>
-      <c r="DT2" t="n">
+      <c r="ER2" t="n">
         <v>28800000</v>
       </c>
-      <c r="DU2" t="inlineStr">
+      <c r="ES2" t="inlineStr">
         <is>
           <t>cn_market</t>
         </is>
       </c>
-      <c r="DV2" t="b">
+      <c r="ET2" t="b">
         <v>0</v>
       </c>
-      <c r="DW2" t="n">
+      <c r="EU2" t="b">
         <v>0</v>
       </c>
-      <c r="DX2" t="n">
-        <v>4.89</v>
-      </c>
-      <c r="DY2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
-      </c>
-      <c r="DZ2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EA2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EB2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EC2" t="b">
-        <v>0</v>
-      </c>
-      <c r="ED2" t="n">
+      <c r="EV2" t="n">
         <v>1088472600000</v>
-      </c>
-      <c r="EE2" t="n">
-        <v>0</v>
-      </c>
-      <c r="EF2" t="inlineStr">
-        <is>
-          <t>4.72 - 4.89</t>
-        </is>
-      </c>
-      <c r="EG2" t="inlineStr">
-        <is>
-          <t>Shenzhen</t>
-        </is>
-      </c>
-      <c r="EH2" t="n">
-        <v>23143759</v>
-      </c>
-      <c r="EI2" t="n">
-        <v>0.17000008</v>
-      </c>
-      <c r="EJ2" t="n">
-        <v>0.036016967</v>
-      </c>
-      <c r="EK2" t="inlineStr">
-        <is>
-          <t>4.72 - 7.39</t>
-        </is>
-      </c>
-      <c r="EL2" t="n">
-        <v>-2.5</v>
-      </c>
-      <c r="EM2" t="n">
-        <v>-0.338295</v>
-      </c>
-      <c r="EN2" t="n">
-        <v>-7.3863626</v>
-      </c>
-      <c r="EO2" t="n">
-        <v>1651229940</v>
-      </c>
-      <c r="EP2" t="n">
-        <v>1651492800</v>
-      </c>
-      <c r="EQ2" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="ER2" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="ES2" t="n">
-        <v>-0.6010003</v>
-      </c>
-      <c r="ET2" t="n">
-        <v>-0.10945188</v>
-      </c>
-      <c r="EU2" t="n">
-        <v>-1.14575</v>
-      </c>
-      <c r="EV2" t="n">
-        <v>-0.1898273</v>
       </c>
       <c r="EW2" t="inlineStr"/>
     </row>
